--- a/balance/NinjaMod_Balance.xlsx
+++ b/balance/NinjaMod_Balance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\--UnityProject\RunminG-Lab\SlaytheSpire2_mod\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC56AA50-AC4B-41D3-95A4-A95F7B252B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12961CEC-CBD8-4294-91B7-A68F1E6F9745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{E1875C0B-A6BC-4540-87E7-A85DB8E4E18A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{E1875C0B-A6BC-4540-87E7-A85DB8E4E18A}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="5" r:id="rId1"/>
@@ -8052,7 +8052,7 @@
         <v>6</v>
       </c>
       <c r="BA19" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB19" s="12"/>
       <c r="BC19" s="12"/>
@@ -8162,7 +8162,9 @@
       <c r="AZ20" s="12">
         <v>9</v>
       </c>
-      <c r="BA20" s="12"/>
+      <c r="BA20" s="12">
+        <v>11</v>
+      </c>
       <c r="BB20" s="12"/>
       <c r="BC20" s="12"/>
       <c r="BD20" s="12"/>

--- a/balance/NinjaMod_Balance.xlsx
+++ b/balance/NinjaMod_Balance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\--UnityProject\RunminG-Lab\SlaytheSpire2_mod\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12961CEC-CBD8-4294-91B7-A68F1E6F9745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372737D-D536-494B-9A28-FEDF5096B330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{E1875C0B-A6BC-4540-87E7-A85DB8E4E18A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{E1875C0B-A6BC-4540-87E7-A85DB8E4E18A}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="5" r:id="rId1"/>
@@ -2193,7 +2193,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2248,6 +2248,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2281,7 +2287,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2335,6 +2341,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4265,7 +4274,7 @@
       <c r="I49" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="4" t="s">
+      <c r="J49" s="18" t="s">
         <v>185</v>
       </c>
     </row>

--- a/balance/NinjaMod_Balance.xlsx
+++ b/balance/NinjaMod_Balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\--UnityProject\RunminG-Lab\SlaytheSpire2_mod\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372737D-D536-494B-9A28-FEDF5096B330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D320F2E-0DBD-45BE-A2B6-A6BFA0FDC0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{E1875C0B-A6BC-4540-87E7-A85DB8E4E18A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="696">
   <si>
     <t>用途</t>
   </si>
@@ -2129,6 +2129,26 @@
   </si>
   <si>
     <t>造成 7(11) 点伤害，附加 2 层【流血】。【武藏】牌。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追魂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对目标打出消耗牌堆中的所有【飞刀】（每张造成其伤害+流血）；若成功击杀，抽 2(3) 张牌。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁镰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成 9(12) 点伤害；若目标有【流血】，额外造成 4(6) 点伤害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得 3(4) 层【淬火】：本回合攻击牌每次造成伤害额外附加等同于淬火层数的【燃烧】。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2287,7 +2307,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2344,6 +2364,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2837,7 +2860,7 @@
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>33</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -4202,8 +4225,8 @@
       <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>177</v>
+      <c r="F47" s="18" t="s">
+        <v>693</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>178</v>
@@ -4212,8 +4235,8 @@
         <v>178</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="4" t="s">
-        <v>179</v>
+      <c r="J47" s="19" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4262,8 +4285,8 @@
       <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>183</v>
+      <c r="F49" s="18" t="s">
+        <v>691</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>184</v>
@@ -4275,7 +4298,7 @@
         <v>45</v>
       </c>
       <c r="J49" s="18" t="s">
-        <v>185</v>
+        <v>692</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="29" x14ac:dyDescent="0.3">

--- a/balance/NinjaMod_Balance.xlsx
+++ b/balance/NinjaMod_Balance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\__RunminG-Lab\SlaytheSpire2_mod\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD61040E-FFD2-4305-8D54-1330CE58B304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82CB2CE6-1CDB-4EB7-84A5-47F03720FC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{F9B761CB-8BAA-4208-8885-F2E68FD70C6F}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{5A12750B-E6DB-4A4C-98D0-2B3CA8B56BA9}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="5" r:id="rId1"/>
@@ -464,7 +464,7 @@
     <t>MusashiCrimson</t>
   </si>
   <si>
-    <t>获得 2 层【淬火】。</t>
+    <t>获得 2(3) 层【淬火】。</t>
   </si>
   <si>
     <t>武藏：迅光三角剑</t>
@@ -668,7 +668,7 @@
     <t>BoneArt</t>
   </si>
   <si>
-    <t>获得 11 点格挡，并获得 2 点【活力】。</t>
+    <t>获得 11(15) 点格挡，并获得 2(3) 点【活力】。</t>
   </si>
   <si>
     <t>九字护身法</t>
@@ -1727,7 +1727,7 @@
     <t>常量变量，保持 JSON 格式。</t>
   </si>
   <si>
-    <t>{"Vigor": 2}</t>
+    <t>{"Vigor": 2, "VigorUpgraded": 3}</t>
   </si>
   <si>
     <t>{"Count": 2}</t>
@@ -2905,7 +2905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7826F2A5-C417-4819-A760-8F02386D98B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC746EB-6BED-40CF-8672-F25B09236A0D}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3004,7 +3004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFC82F3-802E-4747-A3CF-11B47B8E7849}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F4D94A-EA2D-49D3-9C90-B48D4E863FA5}">
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4261,7 +4261,7 @@
         <v>78</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E41" s="9">
         <v>2</v>
@@ -5409,93 +5409,93 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J78" xr:uid="{9AFC82F3-802E-4747-A3CF-11B47B8E7849}"/>
+  <autoFilter ref="A1:J78" xr:uid="{82F4D94A-EA2D-49D3-9C90-B48D4E863FA5}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A8" location="'卡牌数值'!D$1" display="打开" xr:uid="{16D74CA3-8BD6-4124-AEEC-B2D89C9724A2}"/>
-    <hyperlink ref="A7" location="'卡牌数值'!E$1" display="打开" xr:uid="{D9C60434-E0B3-47B4-9D67-6D246B1243E9}"/>
-    <hyperlink ref="A57" location="'卡牌数值'!F$1" display="打开" xr:uid="{181DDF4A-7237-4D5C-AED5-3ABA3D8ED95C}"/>
-    <hyperlink ref="A25" location="'卡牌数值'!G$1" display="打开" xr:uid="{C3A4FFC7-1E49-4824-9B94-2A2DC1F1555F}"/>
-    <hyperlink ref="A6" location="'卡牌数值'!H$1" display="打开" xr:uid="{2FE3C26B-AD59-4DC5-A790-1790396C8A30}"/>
-    <hyperlink ref="A10" location="'卡牌数值'!I$1" display="打开" xr:uid="{A4D61A3F-3F94-4390-BFCD-122A802AEBFB}"/>
-    <hyperlink ref="A26" location="'卡牌数值'!J$1" display="打开" xr:uid="{CEB3C2E8-C072-476A-8442-53FE9DF8290E}"/>
-    <hyperlink ref="A28" location="'卡牌数值'!K$1" display="打开" xr:uid="{A8B969B4-AF29-4DCE-A053-61745F74AF91}"/>
-    <hyperlink ref="A11" location="'卡牌数值'!L$1" display="打开" xr:uid="{2514AAF7-904A-41CB-9232-9A8514311331}"/>
-    <hyperlink ref="A9" location="'卡牌数值'!M$1" display="打开" xr:uid="{FB807F28-2B40-4D24-BF6C-C64A18CCD4B3}"/>
-    <hyperlink ref="A58" location="'卡牌数值'!N$1" display="打开" xr:uid="{55811AA8-905A-4C5C-AF95-04B1E56EC22B}"/>
-    <hyperlink ref="A61" location="'卡牌数值'!O$1" display="打开" xr:uid="{CD43B91F-539A-429B-A0F4-0DD1AB5D5FBC}"/>
-    <hyperlink ref="A62" location="'卡牌数值'!P$1" display="打开" xr:uid="{065C7AFD-A424-4C3A-9512-E56E8D561D8E}"/>
-    <hyperlink ref="A12" location="'卡牌数值'!Q$1" display="打开" xr:uid="{CE97B9BD-C9D1-49E6-84D6-00D1F06B9E90}"/>
-    <hyperlink ref="A32" location="'卡牌数值'!R$1" display="打开" xr:uid="{992F7379-A952-45BB-8759-A0C76D897C69}"/>
-    <hyperlink ref="A37" location="'卡牌数值'!S$1" display="打开" xr:uid="{9DF8DF79-259F-43DE-A120-81B93510C59A}"/>
-    <hyperlink ref="A34" location="'卡牌数值'!T$1" display="打开" xr:uid="{CA5EB6FC-7963-442F-B773-A52EF1FACD5D}"/>
-    <hyperlink ref="A36" location="'卡牌数值'!U$1" display="打开" xr:uid="{229F83EE-EE49-43E4-AA53-6E173867CA32}"/>
-    <hyperlink ref="A27" location="'卡牌数值'!V$1" display="打开" xr:uid="{F0B10ADA-3C73-462A-91EE-0731B070D3EF}"/>
-    <hyperlink ref="A24" location="'卡牌数值'!W$1" display="打开" xr:uid="{748C3290-3F4A-433D-8916-440A34A91E85}"/>
-    <hyperlink ref="A59" location="'卡牌数值'!X$1" display="打开" xr:uid="{9E9FA501-15B7-414A-A9F7-949740586E90}"/>
-    <hyperlink ref="A63" location="'卡牌数值'!Y$1" display="打开" xr:uid="{F4960A40-7990-4AA2-9FCE-62CD450F732A}"/>
-    <hyperlink ref="A60" location="'卡牌数值'!Z$1" display="打开" xr:uid="{4988C555-3513-406C-988F-6282B2C20C19}"/>
-    <hyperlink ref="A55" location="'卡牌数值'!AA$1" display="打开" xr:uid="{D522253C-47C7-4DD5-A6C4-919EC705712A}"/>
-    <hyperlink ref="A76" location="'卡牌数值'!AB$1" display="打开" xr:uid="{E978E76E-6E4F-4743-AF8C-4C885E69291A}"/>
-    <hyperlink ref="A78" location="'卡牌数值'!AC$1" display="打开" xr:uid="{6B079010-2F2D-41C2-92BA-296ADBE7C057}"/>
-    <hyperlink ref="A77" location="'卡牌数值'!AD$1" display="打开" xr:uid="{C22BF1E1-3E0D-441F-BBAC-797334FA9A49}"/>
-    <hyperlink ref="A67" location="'卡牌数值'!AE$1" display="打开" xr:uid="{0CB32956-8A95-4087-BDE3-3996580685BE}"/>
-    <hyperlink ref="A65" location="'卡牌数值'!AF$1" display="打开" xr:uid="{0653DC4B-1889-4812-8BFA-27EF259C30B5}"/>
-    <hyperlink ref="A66" location="'卡牌数值'!AG$1" display="打开" xr:uid="{B86134C2-BA49-4B11-A97E-0CD15104FC3E}"/>
-    <hyperlink ref="A17" location="'卡牌数值'!AH$1" display="打开" xr:uid="{CE609D39-D076-457D-96CE-C7789FC1A080}"/>
-    <hyperlink ref="A70" location="'卡牌数值'!AI$1" display="打开" xr:uid="{10FD33C8-93A0-4304-94C8-0654719120F7}"/>
-    <hyperlink ref="A38" location="'卡牌数值'!AJ$1" display="打开" xr:uid="{891AFAB3-5907-446B-8D39-98C3570F2D61}"/>
-    <hyperlink ref="A41" location="'卡牌数值'!AK$1" display="打开" xr:uid="{1A69FCB4-E4B7-4ED3-AF80-9A011C8B4F97}"/>
-    <hyperlink ref="A39" location="'卡牌数值'!AL$1" display="打开" xr:uid="{0FB2112B-7526-43B1-899F-511A75320426}"/>
-    <hyperlink ref="A40" location="'卡牌数值'!AM$1" display="打开" xr:uid="{CCDAE4F1-5587-49FD-969D-69C34161EE56}"/>
-    <hyperlink ref="A68" location="'卡牌数值'!AN$1" display="打开" xr:uid="{EE1E3F19-EBAD-4711-840C-27EC6549A121}"/>
-    <hyperlink ref="A73" location="'卡牌数值'!AO$1" display="打开" xr:uid="{A04A6C22-EBFE-4D6B-A865-3F5BAC22EB60}"/>
-    <hyperlink ref="A75" location="'卡牌数值'!AP$1" display="打开" xr:uid="{048BD626-B4FA-4F7D-B261-DD66C8D78C44}"/>
-    <hyperlink ref="A72" location="'卡牌数值'!AQ$1" display="打开" xr:uid="{4216D299-AD93-4124-9964-304957FCDB6D}"/>
-    <hyperlink ref="A71" location="'卡牌数值'!AR$1" display="打开" xr:uid="{2FE198F4-811C-4E18-8255-B9C873CF1D25}"/>
-    <hyperlink ref="A5" location="'卡牌数值'!AS$1" display="打开" xr:uid="{56425AA4-0AAD-4F0E-8F11-7908379303B1}"/>
-    <hyperlink ref="A22" location="'卡牌数值'!AT$1" display="打开" xr:uid="{F0A120E9-9230-49E8-A4A1-7EB2C9DA9DAF}"/>
-    <hyperlink ref="A23" location="'卡牌数值'!AU$1" display="打开" xr:uid="{E57953F7-555E-433D-89DC-C68EA340144C}"/>
-    <hyperlink ref="A3" location="'卡牌数值'!AV$1" display="打开" xr:uid="{C3DE20FA-355D-40F3-93B8-1E5A8D446D5E}"/>
-    <hyperlink ref="A48" location="'卡牌数值'!AW$1" display="打开" xr:uid="{1CE0DB34-3C9D-412F-B652-E69C5A7854B8}"/>
-    <hyperlink ref="A53" location="'卡牌数值'!AX$1" display="打开" xr:uid="{DBA1DDCA-8E02-4F46-B434-028F0E52B1C5}"/>
-    <hyperlink ref="A50" location="'卡牌数值'!AY$1" display="打开" xr:uid="{2128C8FD-4A29-4C72-A65D-8D9AF0FC040B}"/>
-    <hyperlink ref="A49" location="'卡牌数值'!AZ$1" display="打开" xr:uid="{13087FB2-16CF-4C37-8E6F-D7BEE993B3ED}"/>
-    <hyperlink ref="A31" location="'卡牌数值'!BA$1" display="打开" xr:uid="{D7CE26A5-3C5B-462A-B736-C4C08D79FBBF}"/>
-    <hyperlink ref="A51" location="'卡牌数值'!BB$1" display="打开" xr:uid="{A40C4579-95D4-47CF-8B43-9CE1A2EC45AF}"/>
-    <hyperlink ref="A2" location="'卡牌数值'!BC$1" display="打开" xr:uid="{D09A3A57-E0D8-4372-B73D-8AC3DFD6D268}"/>
-    <hyperlink ref="A21" location="'卡牌数值'!BD$1" display="打开" xr:uid="{87F7D405-3F8D-47BA-93E9-7875D1DF644D}"/>
-    <hyperlink ref="A20" location="'卡牌数值'!BE$1" display="打开" xr:uid="{07239B15-878C-4D94-9983-BC2893F0C41C}"/>
-    <hyperlink ref="A19" location="'卡牌数值'!BF$1" display="打开" xr:uid="{487BFC69-9EC7-45C4-AB51-63AAC245F480}"/>
-    <hyperlink ref="A54" location="'卡牌数值'!BG$1" display="打开" xr:uid="{9F017C27-92C0-45FC-800C-6A4846143D7C}"/>
-    <hyperlink ref="A43" location="'卡牌数值'!BH$1" display="打开" xr:uid="{7FD1B1F0-11D3-4A79-8DE1-913318CAAA98}"/>
-    <hyperlink ref="A45" location="'卡牌数值'!BI$1" display="打开" xr:uid="{E4266A66-6F1A-421C-BCD1-E4CA60C1D84C}"/>
-    <hyperlink ref="A44" location="'卡牌数值'!BJ$1" display="打开" xr:uid="{1C2E34BA-6512-4719-9C80-31F198005E3E}"/>
-    <hyperlink ref="A46" location="'卡牌数值'!BK$1" display="打开" xr:uid="{E60D8A20-A397-44C2-953F-B7EADBD57AFE}"/>
-    <hyperlink ref="A52" location="'卡牌数值'!BL$1" display="打开" xr:uid="{4D738EAB-1603-4620-8B0C-C1B37508A2A4}"/>
-    <hyperlink ref="A47" location="'卡牌数值'!BM$1" display="打开" xr:uid="{838CE5BC-D018-49CE-BE0F-3DD8EB058170}"/>
-    <hyperlink ref="A4" location="'卡牌数值'!BN$1" display="打开" xr:uid="{CD335897-01E3-4732-A8BE-67CD55B30244}"/>
-    <hyperlink ref="A15" location="'卡牌数值'!BO$1" display="打开" xr:uid="{3203C171-FB88-40F2-8435-C2BB62558702}"/>
-    <hyperlink ref="A14" location="'卡牌数值'!BP$1" display="打开" xr:uid="{C855F57C-3BC5-4CF5-A5AE-CEEC76175F52}"/>
-    <hyperlink ref="A33" location="'卡牌数值'!BQ$1" display="打开" xr:uid="{BCE6EAEA-DAAC-4D8D-9D5B-81D6D3748748}"/>
-    <hyperlink ref="A35" location="'卡牌数值'!BR$1" display="打开" xr:uid="{921787FE-34DE-4AF9-83ED-702BA9E2CF53}"/>
-    <hyperlink ref="A56" location="'卡牌数值'!BS$1" display="打开" xr:uid="{475E4CFE-A743-4749-AE69-80D0F60BA7AE}"/>
-    <hyperlink ref="A13" location="'卡牌数值'!BT$1" display="打开" xr:uid="{2EC3609E-42EC-4D05-8496-E1B6BAB53DB2}"/>
-    <hyperlink ref="A30" location="'卡牌数值'!BU$1" display="打开" xr:uid="{800375FC-98A4-463D-97E0-EF79059D7097}"/>
-    <hyperlink ref="A42" location="'卡牌数值'!BV$1" display="打开" xr:uid="{F48A7DFB-DC74-43AB-9B29-79627B1BA1F8}"/>
-    <hyperlink ref="A18" location="'卡牌数值'!BW$1" display="打开" xr:uid="{A28BC9AF-2A8C-4A23-B65F-F03E6CF936C7}"/>
-    <hyperlink ref="A74" location="'卡牌数值'!BX$1" display="打开" xr:uid="{A10FE843-E334-46B9-92F6-F0551D29907B}"/>
-    <hyperlink ref="A69" location="'卡牌数值'!BY$1" display="打开" xr:uid="{72B43B24-324F-46F3-994B-EF2CC511B08D}"/>
-    <hyperlink ref="A64" location="'卡牌数值'!BZ$1" display="打开" xr:uid="{01DD12FF-43E3-4277-AE03-630B5C42B9B8}"/>
-    <hyperlink ref="A16" location="'卡牌数值'!CA$1" display="打开" xr:uid="{83DEA829-00B0-4AD8-A0E0-E8F64B8F43B6}"/>
-    <hyperlink ref="A29" location="'卡牌数值'!CB$1" display="打开" xr:uid="{B2F36BF5-FDFE-4921-93DD-08195170C203}"/>
+    <hyperlink ref="A8" location="'卡牌数值'!D$1" display="打开" xr:uid="{A26CD4CB-31B4-4348-9862-F81E8BB1F432}"/>
+    <hyperlink ref="A7" location="'卡牌数值'!E$1" display="打开" xr:uid="{E614DDDC-AAB6-4586-BBDA-76C4222DF317}"/>
+    <hyperlink ref="A57" location="'卡牌数值'!F$1" display="打开" xr:uid="{9B10917D-D84A-43D5-8B18-663A7F00CC3E}"/>
+    <hyperlink ref="A25" location="'卡牌数值'!G$1" display="打开" xr:uid="{4B12EDA5-93B2-4D7F-9B0B-5C2E13FE77A1}"/>
+    <hyperlink ref="A6" location="'卡牌数值'!H$1" display="打开" xr:uid="{FF334929-3AB3-4120-AC34-7FFCEFA683A1}"/>
+    <hyperlink ref="A10" location="'卡牌数值'!I$1" display="打开" xr:uid="{BFE3CB6C-1043-460C-95EE-0A2B8A1AC96A}"/>
+    <hyperlink ref="A26" location="'卡牌数值'!J$1" display="打开" xr:uid="{9F3DA9CB-481A-4321-8DDA-F7DC7102F876}"/>
+    <hyperlink ref="A28" location="'卡牌数值'!K$1" display="打开" xr:uid="{03939E20-8412-4D1A-A36D-C3C8DAE405D5}"/>
+    <hyperlink ref="A11" location="'卡牌数值'!L$1" display="打开" xr:uid="{5C481514-173F-4B4D-8CCE-02F205B21B81}"/>
+    <hyperlink ref="A9" location="'卡牌数值'!M$1" display="打开" xr:uid="{357F9C15-F97E-4260-86C7-BF038CAEF5A4}"/>
+    <hyperlink ref="A58" location="'卡牌数值'!N$1" display="打开" xr:uid="{7F053C80-B4CF-48A2-AD27-3627930B9899}"/>
+    <hyperlink ref="A61" location="'卡牌数值'!O$1" display="打开" xr:uid="{2075C932-6166-407A-AF16-68BF37EBDFF9}"/>
+    <hyperlink ref="A62" location="'卡牌数值'!P$1" display="打开" xr:uid="{CB45D135-35B9-440A-B2A2-73C562AD780A}"/>
+    <hyperlink ref="A12" location="'卡牌数值'!Q$1" display="打开" xr:uid="{75FF8EE8-B92C-442D-B1E6-5EF85D5572F6}"/>
+    <hyperlink ref="A32" location="'卡牌数值'!R$1" display="打开" xr:uid="{19FE2B8F-76B5-4783-94B6-F1520ED4B5D0}"/>
+    <hyperlink ref="A37" location="'卡牌数值'!S$1" display="打开" xr:uid="{B4E2B47A-10AB-41B8-8283-F6AFCC250049}"/>
+    <hyperlink ref="A34" location="'卡牌数值'!T$1" display="打开" xr:uid="{E2D8224B-EE87-4270-AE35-306785DE8932}"/>
+    <hyperlink ref="A36" location="'卡牌数值'!U$1" display="打开" xr:uid="{27FA45C3-16F5-4EC0-977B-1C5871FBF7F7}"/>
+    <hyperlink ref="A27" location="'卡牌数值'!V$1" display="打开" xr:uid="{916244A8-DC41-4BD3-B929-4934CE4B7608}"/>
+    <hyperlink ref="A24" location="'卡牌数值'!W$1" display="打开" xr:uid="{24078FE3-3702-4CEF-B2B9-3E434CF5280F}"/>
+    <hyperlink ref="A59" location="'卡牌数值'!X$1" display="打开" xr:uid="{5551E71A-9DB7-4904-9CD3-EABE84D8775D}"/>
+    <hyperlink ref="A63" location="'卡牌数值'!Y$1" display="打开" xr:uid="{938A46A7-C6FA-4FF3-B918-B9D6D3C0D2D3}"/>
+    <hyperlink ref="A60" location="'卡牌数值'!Z$1" display="打开" xr:uid="{AFF940A6-AEB8-4972-89D9-34A893B18326}"/>
+    <hyperlink ref="A55" location="'卡牌数值'!AA$1" display="打开" xr:uid="{C14FA6A4-8257-4E50-84BE-BE8F1F6A6E0E}"/>
+    <hyperlink ref="A76" location="'卡牌数值'!AB$1" display="打开" xr:uid="{0B2AC667-F74B-42A2-A345-5EF1022C4198}"/>
+    <hyperlink ref="A78" location="'卡牌数值'!AC$1" display="打开" xr:uid="{804F9EE2-3303-42C4-BD70-5EE55C56EF61}"/>
+    <hyperlink ref="A77" location="'卡牌数值'!AD$1" display="打开" xr:uid="{95F81A51-18F3-4506-AFCC-9A966B8CADC3}"/>
+    <hyperlink ref="A67" location="'卡牌数值'!AE$1" display="打开" xr:uid="{50FBCF09-289E-43D8-B991-6507940F89B2}"/>
+    <hyperlink ref="A65" location="'卡牌数值'!AF$1" display="打开" xr:uid="{BA40D10E-6A6D-4C71-9320-C39025038B8A}"/>
+    <hyperlink ref="A66" location="'卡牌数值'!AG$1" display="打开" xr:uid="{E7359133-6DF4-4BB5-8159-4EBEAE45F573}"/>
+    <hyperlink ref="A17" location="'卡牌数值'!AH$1" display="打开" xr:uid="{AB91E30C-A5D7-4E7A-A61D-41A3E0D35D08}"/>
+    <hyperlink ref="A70" location="'卡牌数值'!AI$1" display="打开" xr:uid="{926107FF-A01A-4B95-932D-0584C00F628A}"/>
+    <hyperlink ref="A38" location="'卡牌数值'!AJ$1" display="打开" xr:uid="{F5DBD22A-02C9-40EC-BC99-77935BA64D70}"/>
+    <hyperlink ref="A41" location="'卡牌数值'!AK$1" display="打开" xr:uid="{45592DD4-8458-41AE-A9EC-7EF169D236BD}"/>
+    <hyperlink ref="A39" location="'卡牌数值'!AL$1" display="打开" xr:uid="{727F22BB-146F-4079-A44F-B06D97D4AC09}"/>
+    <hyperlink ref="A40" location="'卡牌数值'!AM$1" display="打开" xr:uid="{951AF928-7F47-479C-AE1E-069EE9003DA2}"/>
+    <hyperlink ref="A68" location="'卡牌数值'!AN$1" display="打开" xr:uid="{DA51AC90-26DC-400D-9D14-D5F1F468B4C0}"/>
+    <hyperlink ref="A73" location="'卡牌数值'!AO$1" display="打开" xr:uid="{AB970096-ABF3-4F48-87B5-B66A9C0E2CBE}"/>
+    <hyperlink ref="A75" location="'卡牌数值'!AP$1" display="打开" xr:uid="{C8EF8F37-3AAB-456B-8D89-241296B5D9D9}"/>
+    <hyperlink ref="A72" location="'卡牌数值'!AQ$1" display="打开" xr:uid="{EE5E7272-26E1-4E03-8096-0B1593675822}"/>
+    <hyperlink ref="A71" location="'卡牌数值'!AR$1" display="打开" xr:uid="{B4E54A05-6E17-4CFD-8D18-682238136783}"/>
+    <hyperlink ref="A5" location="'卡牌数值'!AS$1" display="打开" xr:uid="{98D4FC13-1FC4-48C1-B0E2-CF7572E5D753}"/>
+    <hyperlink ref="A22" location="'卡牌数值'!AT$1" display="打开" xr:uid="{0883F911-6734-4004-9977-115BD16EA24E}"/>
+    <hyperlink ref="A23" location="'卡牌数值'!AU$1" display="打开" xr:uid="{544FF932-B903-4FA2-B2C6-F94A8EAA31F3}"/>
+    <hyperlink ref="A3" location="'卡牌数值'!AV$1" display="打开" xr:uid="{884E4BFA-69A1-4577-BEDA-F61BA2E51007}"/>
+    <hyperlink ref="A48" location="'卡牌数值'!AW$1" display="打开" xr:uid="{C8C86A84-EBD6-4C21-BC3E-6CEA23319579}"/>
+    <hyperlink ref="A53" location="'卡牌数值'!AX$1" display="打开" xr:uid="{A3A7FC62-0223-4D04-8470-F44C53AFFEF7}"/>
+    <hyperlink ref="A50" location="'卡牌数值'!AY$1" display="打开" xr:uid="{B911F6B2-ECA8-4845-A1E7-260D3B60DB8B}"/>
+    <hyperlink ref="A49" location="'卡牌数值'!AZ$1" display="打开" xr:uid="{734850AF-E3DB-4456-A2F0-09C56662670B}"/>
+    <hyperlink ref="A31" location="'卡牌数值'!BA$1" display="打开" xr:uid="{E43A6D34-A76F-404A-9AC5-404245F3D0B1}"/>
+    <hyperlink ref="A51" location="'卡牌数值'!BB$1" display="打开" xr:uid="{DBB7009C-E32C-4F9F-9815-FABFAEF1CFAE}"/>
+    <hyperlink ref="A2" location="'卡牌数值'!BC$1" display="打开" xr:uid="{4F4671B2-B564-4B02-831C-A23383DDE16B}"/>
+    <hyperlink ref="A21" location="'卡牌数值'!BD$1" display="打开" xr:uid="{92449BD4-4D9E-4E6F-959D-A6F34DF34540}"/>
+    <hyperlink ref="A20" location="'卡牌数值'!BE$1" display="打开" xr:uid="{2C377A93-071F-4BF8-9DE1-E2F0CD039118}"/>
+    <hyperlink ref="A19" location="'卡牌数值'!BF$1" display="打开" xr:uid="{A52B49A0-7965-4AB3-93AC-E9A2D950450F}"/>
+    <hyperlink ref="A54" location="'卡牌数值'!BG$1" display="打开" xr:uid="{AE45E290-568A-4F69-8C78-F9D7C0AE1823}"/>
+    <hyperlink ref="A43" location="'卡牌数值'!BH$1" display="打开" xr:uid="{BA91948E-BAEE-4156-BDD8-086C934B7277}"/>
+    <hyperlink ref="A45" location="'卡牌数值'!BI$1" display="打开" xr:uid="{61527EF7-98E9-438F-92F6-C69BE985E2CC}"/>
+    <hyperlink ref="A44" location="'卡牌数值'!BJ$1" display="打开" xr:uid="{D98E6492-E974-4797-A3C1-A653A44D7E2A}"/>
+    <hyperlink ref="A46" location="'卡牌数值'!BK$1" display="打开" xr:uid="{F1F00C3A-BE13-484F-A76E-0B3BA8B0C3FC}"/>
+    <hyperlink ref="A52" location="'卡牌数值'!BL$1" display="打开" xr:uid="{B0ED6633-A18C-4169-A6A1-9A7EBB7FE0D3}"/>
+    <hyperlink ref="A47" location="'卡牌数值'!BM$1" display="打开" xr:uid="{609732F7-D2CC-4A24-A626-FD641ACC6D6D}"/>
+    <hyperlink ref="A4" location="'卡牌数值'!BN$1" display="打开" xr:uid="{EFEF80F1-86D8-478D-84BB-1288F62A68B0}"/>
+    <hyperlink ref="A15" location="'卡牌数值'!BO$1" display="打开" xr:uid="{1C6FED27-915E-478E-9643-DD9488516FBE}"/>
+    <hyperlink ref="A14" location="'卡牌数值'!BP$1" display="打开" xr:uid="{5FFBEC32-02F0-4956-B1BC-1567D87129C6}"/>
+    <hyperlink ref="A33" location="'卡牌数值'!BQ$1" display="打开" xr:uid="{104350DA-59F4-4392-AC6D-79471FA9214D}"/>
+    <hyperlink ref="A35" location="'卡牌数值'!BR$1" display="打开" xr:uid="{B8E57C5C-3DFD-4592-8E4C-448C0E49C46E}"/>
+    <hyperlink ref="A56" location="'卡牌数值'!BS$1" display="打开" xr:uid="{B88F6C0B-B0A0-4525-B883-CA55AA43D751}"/>
+    <hyperlink ref="A13" location="'卡牌数值'!BT$1" display="打开" xr:uid="{C8279948-F421-443A-99CD-90A92AAF15EC}"/>
+    <hyperlink ref="A30" location="'卡牌数值'!BU$1" display="打开" xr:uid="{9892057E-6828-4E38-BA76-A9427AE8F6BB}"/>
+    <hyperlink ref="A42" location="'卡牌数值'!BV$1" display="打开" xr:uid="{01E371DC-B222-4E6D-BA1E-6454C2AFD7E5}"/>
+    <hyperlink ref="A18" location="'卡牌数值'!BW$1" display="打开" xr:uid="{DFF53BFC-5C03-4ED0-81C2-97F1ADED3A59}"/>
+    <hyperlink ref="A74" location="'卡牌数值'!BX$1" display="打开" xr:uid="{847C8C97-F6A2-44EA-92F9-83891ED67DF3}"/>
+    <hyperlink ref="A69" location="'卡牌数值'!BY$1" display="打开" xr:uid="{52A61958-7E12-474B-8FF4-A98C6BC4E35A}"/>
+    <hyperlink ref="A64" location="'卡牌数值'!BZ$1" display="打开" xr:uid="{2433F839-C576-4850-A4A6-88C4EBBAE338}"/>
+    <hyperlink ref="A16" location="'卡牌数值'!CA$1" display="打开" xr:uid="{B3CFF3A1-6F76-4D90-A0AB-5D86882A2971}"/>
+    <hyperlink ref="A29" location="'卡牌数值'!CB$1" display="打开" xr:uid="{C348F711-1400-434A-9E65-B9768DC1B735}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F953D376-2557-4FFE-A3D2-588E7C73D0D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72001FFE-9B33-4D7C-A446-13BC21F96CC7}">
   <dimension ref="A1:CB89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6342,7 +6342,7 @@
         <v>30</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL4" s="11" t="s">
         <v>30</v>
@@ -8008,7 +8008,7 @@
         <v>30</v>
       </c>
       <c r="AK11" s="14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL11" s="14" t="s">
         <v>30</v>
@@ -9908,7 +9908,9 @@
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="F22" s="15">
+        <v>15</v>
+      </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
@@ -14280,7 +14282,9 @@
       <c r="BO69" s="15"/>
       <c r="BP69" s="15"/>
       <c r="BQ69" s="15"/>
-      <c r="BR69" s="15"/>
+      <c r="BR69" s="15">
+        <v>3</v>
+      </c>
       <c r="BS69" s="15"/>
       <c r="BT69" s="15"/>
       <c r="BU69" s="15"/>
@@ -15038,7 +15042,7 @@
       <c r="CA77" s="15"/>
       <c r="CB77" s="15"/>
     </row>
-    <row r="78" spans="1:80" ht="58" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:80" ht="72.5" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>561</v>
       </c>
@@ -16721,7 +16725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E28E3187-D08D-4CF7-8F0F-F2A2D1213499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8C27C0-327A-4BD6-AF82-3A6BF51D7516}">
   <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17911,7 +17915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99EF2DB-C638-45E5-924F-240A85917DD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FDAE2B4-2075-44CD-BE6D-8EC119551F35}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
